--- a/Result/profitability/6290.xlsx
+++ b/Result/profitability/6290.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8</v>
+        <v>1.935</v>
       </c>
       <c r="N2" t="n">
-        <v>26.99875</v>
+        <v>28.28</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>1.79875</v>
+        <v>1.76375</v>
       </c>
       <c r="N3" t="n">
-        <v>26.2875</v>
+        <v>26.615</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.74</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6275</v>
+        <v>1.53625</v>
       </c>
       <c r="N4" t="n">
-        <v>24.45375</v>
+        <v>24.55125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>1.28875</v>
+        <v>1.385</v>
       </c>
       <c r="N5" t="n">
-        <v>21.96875</v>
+        <v>21.8675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2675</v>
+        <v>1.175</v>
       </c>
       <c r="N6" t="n">
-        <v>20.76875</v>
+        <v>20.79</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.07</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>0.9837500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>20.22</v>
+        <v>19.65</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.93625</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>18.8725</v>
+        <v>18.7525</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2696</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1881</v>
+      </c>
+      <c r="E75" t="n">
+        <v>815</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>428</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>439</v>
+      </c>
+      <c r="K75" t="n">
+        <v>310</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.29375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3171641791044776</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9600000000000009</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03077909586405903</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7264150943396226</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8099999999999987</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02609536082474218</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
